--- a/template.xlsx
+++ b/template.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">시트1!$A$9:$AA$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'시트3 스티커 발행'!$A$2:$J$6</definedName>
-    <definedName name="Excel_BuiltIn__FilterDatabase_1">'시트2 32품목 스티커'!$A$1:$X$2</definedName>
+    <definedName name="Excel_BuiltIn__FilterDatabase_1">'시트2 32품목 스티커'!$A$1:$X$17</definedName>
     <definedName name="Excel_BuiltIn_Print_Titles">시트1!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">시트1!$A$1:$M$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">시트1!$9:$9</definedName>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="272">
   <si>
     <t xml:space="preserve">*포는 1포기준 /점안액30A은 1A /ml 통안약은 1통기준 등록 </t>
   </si>
@@ -113,6 +113,9 @@
     <t>구보험코드</t>
   </si>
   <si>
+    <t>28T</t>
+  </si>
+  <si>
     <t>보험(전문)</t>
   </si>
   <si>
@@ -128,19 +131,124 @@
     <t>30T</t>
   </si>
   <si>
+    <t>기타의 중추신경용약</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
+    <t>300T</t>
+  </si>
+  <si>
+    <t>보험(일반)</t>
+  </si>
+  <si>
+    <t>소화성궤양용제</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>30C</t>
+  </si>
+  <si>
+    <t>기타의 화학요법제</t>
+  </si>
+  <si>
     <t>1 정</t>
   </si>
   <si>
+    <t>1 캡슐</t>
+  </si>
+  <si>
+    <t>100T</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>해열.진통.소염제</t>
+  </si>
+  <si>
+    <t>500T</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>esomeprazol magnesium (as esomeprazol   20mg)</t>
+  </si>
+  <si>
+    <t>esomeprazol magnesium (as esomeprazol   40mg)</t>
+  </si>
+  <si>
     <t>혈압강하제</t>
   </si>
   <si>
+    <t>기타의 소화기관용약</t>
+  </si>
+  <si>
+    <t>losartan potassium (as losartan   45.8mg)</t>
+  </si>
+  <si>
+    <t>기타의 혈액 및 체액용약</t>
+  </si>
+  <si>
+    <t>loxoprofen sodium hydrate (as loxoprofen sodium   60mg)</t>
+  </si>
+  <si>
+    <t>따로 분류되지 않은 대사성 의약품</t>
+  </si>
+  <si>
+    <t>동맥경화용제</t>
+  </si>
+  <si>
+    <t>atorvastatin calcium (as atorvastatin   10mg)</t>
+  </si>
+  <si>
+    <t>atorvastatin(calcium) 20mg</t>
+  </si>
+  <si>
+    <t>itraconazole   0.1g</t>
+  </si>
+  <si>
+    <t>mosapride citrate hydrate (as mosapride   5mg)</t>
+  </si>
+  <si>
     <t>정</t>
   </si>
   <si>
+    <t>artemisiae argyi folium 95% ethanol ext.(20→1)   60mg</t>
+  </si>
+  <si>
+    <t>aceclofenac   0.1g</t>
+  </si>
+  <si>
+    <t>골격근이완제</t>
+  </si>
+  <si>
+    <t>eperisone hydrochloride   50mg</t>
+  </si>
+  <si>
+    <t>600T</t>
+  </si>
+  <si>
+    <t>hydrochlorothiazide   12.5mg</t>
+  </si>
+  <si>
+    <t>sarpogrelate Hydrochloride   0.3g</t>
+  </si>
+  <si>
     <t>기타제약사</t>
+  </si>
+  <si>
+    <t>diacerhein 50mg</t>
+  </si>
+  <si>
+    <t>혼합비타민제(비타민AD 혼합제제를 제외)</t>
+  </si>
+  <si>
+    <t>donepezil hydrochloride   23mg</t>
   </si>
   <si>
     <t>불용재고의약품</t>
@@ -202,9 +310,60 @@
     <t>성 분</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>51313</t>
+  </si>
+  <si>
+    <t>한풍제약서울영업소</t>
+  </si>
+  <si>
     <t>(유) 한풍제약</t>
   </si>
   <si>
+    <t>다노펜세미정</t>
+  </si>
+  <si>
+    <t>658106370</t>
+  </si>
+  <si>
+    <t>한풍 다노펜세미정/30T</t>
+  </si>
+  <si>
+    <t>8806581063715</t>
+  </si>
+  <si>
+    <t>51318</t>
+  </si>
+  <si>
+    <t>아세네정</t>
+  </si>
+  <si>
+    <t>658106680</t>
+  </si>
+  <si>
+    <t>한풍 아세네정/30T</t>
+  </si>
+  <si>
+    <t>8806581066815</t>
+  </si>
+  <si>
+    <t>51311</t>
+  </si>
+  <si>
+    <t>다노펜정</t>
+  </si>
+  <si>
+    <t>658106360</t>
+  </si>
+  <si>
+    <t>한풍 다노펜정/30T</t>
+  </si>
+  <si>
+    <t>8806581063616</t>
+  </si>
+  <si>
     <t>51320</t>
   </si>
   <si>
@@ -215,19 +374,348 @@
   </si>
   <si>
     <t>8806581063517</t>
+  </si>
+  <si>
+    <t>51322</t>
+  </si>
+  <si>
+    <t>에이토바정 10mg</t>
+  </si>
+  <si>
+    <t>658106610</t>
+  </si>
+  <si>
+    <t>한풍 에이토바정 10mg/30T</t>
+  </si>
+  <si>
+    <t>8806581066112</t>
+  </si>
+  <si>
+    <t>51305</t>
+  </si>
+  <si>
+    <t>오메나정 20mg</t>
+  </si>
+  <si>
+    <t>658107000</t>
+  </si>
+  <si>
+    <t>한풍 오메나정 20mg/28T</t>
+  </si>
+  <si>
+    <t>8806581070010</t>
+  </si>
+  <si>
+    <t>51306</t>
+  </si>
+  <si>
+    <t>오메나정 40mg</t>
+  </si>
+  <si>
+    <t>658106970</t>
+  </si>
+  <si>
+    <t>한풍 오메나정 40mg/28T</t>
+  </si>
+  <si>
+    <t>8806581069717</t>
+  </si>
+  <si>
+    <t>이코녹스정 100mg</t>
+  </si>
+  <si>
+    <t>658107140</t>
+  </si>
+  <si>
+    <t>51314</t>
+  </si>
+  <si>
+    <t>한풍 다노펜세미정/300T</t>
+  </si>
+  <si>
+    <t>8806581063722</t>
+  </si>
+  <si>
+    <t>51312</t>
+  </si>
+  <si>
+    <t>한풍 다노펜정/300T</t>
+  </si>
+  <si>
+    <t>8806581063623</t>
+  </si>
+  <si>
+    <t>51319</t>
+  </si>
+  <si>
+    <t>한풍 아세네정/500T</t>
+  </si>
+  <si>
+    <t>8806581066822</t>
+  </si>
+  <si>
+    <t>51309</t>
+  </si>
+  <si>
+    <t>한풍 이코녹스정 100mg/100T</t>
+  </si>
+  <si>
+    <t>8806581071420</t>
+  </si>
+  <si>
+    <t>52295</t>
+  </si>
+  <si>
+    <t>658108120</t>
+  </si>
+  <si>
+    <t>한풍 도네일정 23mg/30T</t>
+  </si>
+  <si>
+    <t>52137</t>
+  </si>
+  <si>
+    <t>로사탈정 50mg</t>
+  </si>
+  <si>
+    <t>658106630</t>
+  </si>
+  <si>
+    <t>한풍 로사탈정 50mg/300T</t>
+  </si>
+  <si>
+    <t>8806581066327</t>
+  </si>
+  <si>
+    <t>52136</t>
+  </si>
+  <si>
+    <t>한풍 로사탈정 50mg/30T</t>
+  </si>
+  <si>
+    <t>8806581066310</t>
+  </si>
+  <si>
+    <t>52139</t>
+  </si>
+  <si>
+    <t>에이토바정 20mg</t>
+  </si>
+  <si>
+    <t>658106620</t>
+  </si>
+  <si>
+    <t>한풍 에이토바정 20mg/100T</t>
+  </si>
+  <si>
+    <t>52138</t>
+  </si>
+  <si>
+    <t>한풍 에이토바정 20mg/30T</t>
+  </si>
+  <si>
+    <t>8806581066211</t>
+  </si>
+  <si>
+    <t>53513</t>
+  </si>
+  <si>
+    <t>658106440</t>
+  </si>
+  <si>
+    <t>8806581064422</t>
+  </si>
+  <si>
+    <t>8806581081214</t>
+  </si>
+  <si>
+    <t>53609</t>
+  </si>
+  <si>
+    <t>디세나캅셀 50mg</t>
+  </si>
+  <si>
+    <t>658106460</t>
+  </si>
+  <si>
+    <t>한풍 디세나캅셀 50mg/30C</t>
+  </si>
+  <si>
+    <t>8806581064613</t>
+  </si>
+  <si>
+    <t>53518</t>
+  </si>
+  <si>
+    <t>로사탈플러스정</t>
+  </si>
+  <si>
+    <t>658106490</t>
+  </si>
+  <si>
+    <t>한풍 로사탈플러스정/30T</t>
+  </si>
+  <si>
+    <t>8806581064910</t>
+  </si>
+  <si>
+    <t>53519</t>
+  </si>
+  <si>
+    <t>록소핀정 60mg</t>
+  </si>
+  <si>
+    <t>658106780</t>
+  </si>
+  <si>
+    <t>한풍 록소핀정 60mg/600T</t>
+  </si>
+  <si>
+    <t>8806581067829</t>
+  </si>
+  <si>
+    <t>53687</t>
+  </si>
+  <si>
+    <t>스토렌정</t>
+  </si>
+  <si>
+    <t>658107840</t>
+  </si>
+  <si>
+    <t>한풍 스토렌정/300T</t>
+  </si>
+  <si>
+    <t>8806581078429</t>
+  </si>
+  <si>
+    <t>8806581066228</t>
+  </si>
+  <si>
+    <t>53521</t>
+  </si>
+  <si>
+    <t>에페나정 50mg</t>
+  </si>
+  <si>
+    <t>658106990</t>
+  </si>
+  <si>
+    <t>한풍 에페나정 50mg/300T</t>
+  </si>
+  <si>
+    <t>8806581069922</t>
   </si>
   <si>
     <t>(주)인천약품</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>(주)인천약품</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>30T(병)</t>
+  </si>
+  <si>
+    <t>100T(병)</t>
+  </si>
+  <si>
+    <t>500T(병)</t>
+  </si>
+  <si>
+    <t>300T(병)</t>
+  </si>
+  <si>
+    <t>54440</t>
+  </si>
+  <si>
     <t>28T(PTP)</t>
   </si>
   <si>
+    <t>54691</t>
+  </si>
+  <si>
+    <t>사포레서방정 300mg</t>
+  </si>
+  <si>
+    <t>54692</t>
+  </si>
+  <si>
+    <t>54810</t>
+  </si>
+  <si>
+    <t>록소핀정 80mg</t>
+  </si>
+  <si>
+    <t>658108170</t>
+  </si>
+  <si>
+    <t>8806581081719</t>
+  </si>
+  <si>
+    <t>658107720</t>
+  </si>
+  <si>
+    <t>한풍 사포레서방정 300mg/30T</t>
+  </si>
+  <si>
+    <t>8806581077217</t>
+  </si>
+  <si>
+    <t>한풍 사포레서방정 300mg/100T</t>
+  </si>
+  <si>
+    <t>8806581077224</t>
+  </si>
+  <si>
+    <t>한풍 록소핀정 80mg/30T</t>
+  </si>
+  <si>
+    <t>8806581067812</t>
+  </si>
+  <si>
+    <t>(주)인천약품</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ascorbic acid   60mg 외 8 건</t>
+  </si>
+  <si>
+    <t>acetaminophen   0.1625g 외 1 건</t>
+  </si>
+  <si>
+    <t>acetaminophen   0.325g 외 1 건</t>
+  </si>
+  <si>
     <t>amlodipine besylate (as amlodipine   5mg)</t>
   </si>
   <si>
+    <t>항전간제</t>
+  </si>
+  <si>
+    <t>dexibuprofen   0.3g</t>
+  </si>
+  <si>
+    <t>gabapentin   0.1g</t>
+  </si>
+  <si>
+    <t>donepezil hydrochloride   10mg</t>
+  </si>
+  <si>
+    <t>donepezil hydrochloride   5mg</t>
+  </si>
+  <si>
     <t>자격요법제(비특이성면역원제제를 포함)</t>
+  </si>
+  <si>
+    <t>가스모프정 5mg/</t>
+  </si>
+  <si>
+    <t>네로민정 10mg/</t>
+  </si>
+  <si>
+    <t>한풍 네로민정 10mg/500T</t>
   </si>
   <si>
     <t>기준가격×계산단위</t>
@@ -242,7 +730,91 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>58424</t>
+  </si>
+  <si>
+    <t>58425</t>
+  </si>
+  <si>
+    <t>58474</t>
+  </si>
+  <si>
+    <t>가바페캅셀100mg/</t>
+  </si>
+  <si>
+    <t>덱시네정 300mg</t>
+  </si>
+  <si>
+    <t>658107490</t>
+  </si>
+  <si>
+    <t>8806581074926</t>
+  </si>
+  <si>
+    <t>8806581074919</t>
+  </si>
+  <si>
+    <t>658107300</t>
+  </si>
+  <si>
+    <t>한풍 덱시네정 300mg/300T</t>
+  </si>
+  <si>
+    <t>8806581073028</t>
+  </si>
+  <si>
+    <t>58516</t>
+  </si>
+  <si>
+    <t>한풍 덱시네정 300mg/30T</t>
+  </si>
+  <si>
+    <t>8806581073011</t>
+  </si>
+  <si>
     <t>(품절)한풍 암로다정/30T</t>
+  </si>
+  <si>
+    <t>한풍 가바페캅셀100mg/100T</t>
+  </si>
+  <si>
+    <t>한풍 가바페캅셀100mg/30T</t>
+  </si>
+  <si>
+    <t>한풍 가스모프정 5mg/300T</t>
+  </si>
+  <si>
+    <t>59297</t>
+  </si>
+  <si>
+    <t>59296</t>
+  </si>
+  <si>
+    <t>도네일정 10mg</t>
+  </si>
+  <si>
+    <t>도네일정 23mg/</t>
+  </si>
+  <si>
+    <t>도네일정 5mg</t>
+  </si>
+  <si>
+    <t>658106340</t>
+  </si>
+  <si>
+    <t>한풍 도네일정 10mg/30T</t>
+  </si>
+  <si>
+    <t>8806581063418</t>
+  </si>
+  <si>
+    <t>658106330</t>
+  </si>
+  <si>
+    <t>한풍 도네일정 5mg/30T</t>
+  </si>
+  <si>
+    <t>8806581063319</t>
   </si>
   <si>
     <t>52308</t>
@@ -313,7 +885,7 @@
     <numFmt numFmtId="177" formatCode="yyyy&quot;. &quot;m&quot;. &quot;d\."/>
     <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <name val="돋움"/>
@@ -374,6 +946,13 @@
       <charset val="129"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="돋움"/>
@@ -406,6 +985,14 @@
     <font>
       <sz val="10"/>
       <color indexed="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="12"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
@@ -721,231 +1308,231 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1066,43 +1653,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1114,18 +1701,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1135,8 +1722,29 @@
     <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1144,17 +1752,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="19" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1165,6 +1788,15 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="3" xfId="19" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1198,84 +1830,111 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="12" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="21" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="23" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="37" fontId="19" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="37" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1291,7 +1950,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1306,7 +1965,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1315,7 +1974,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1331,7 +1990,7 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="19" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1363,25 +2022,28 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="21" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -1965,30 +2627,30 @@
   <dimension ref="A1:AA10"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" style="64" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" style="65" customWidth="1"/>
+    <col min="1" max="1" width="5.88671875" style="71" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" style="72" customWidth="1"/>
     <col min="3" max="3" width="8.77734375" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.21875" style="2" customWidth="1"/>
     <col min="5" max="5" width="22.5546875" style="3" customWidth="1"/>
     <col min="6" max="6" width="5.77734375" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.21875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" style="72" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" style="84" customWidth="1"/>
     <col min="9" max="9" width="11.44140625" style="6" customWidth="1"/>
     <col min="10" max="10" width="9.21875" style="7" customWidth="1"/>
-    <col min="11" max="11" width="11" style="114" customWidth="1"/>
+    <col min="11" max="11" width="11" style="138" customWidth="1"/>
     <col min="12" max="12" width="7.21875" style="4" customWidth="1"/>
     <col min="13" max="13" width="9" style="8" customWidth="1"/>
     <col min="14" max="14" width="7.77734375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="9.5546875" style="64" customWidth="1"/>
-    <col min="16" max="16" width="8.33203125" style="120" customWidth="1"/>
-    <col min="17" max="17" width="9.21875" style="64" customWidth="1"/>
+    <col min="15" max="15" width="9.5546875" style="71" customWidth="1"/>
+    <col min="16" max="16" width="8.33203125" style="144" customWidth="1"/>
+    <col min="17" max="17" width="9.21875" style="71" customWidth="1"/>
     <col min="18" max="18" width="26.21875" style="2" customWidth="1"/>
     <col min="19" max="19" width="8.33203125" style="1" customWidth="1"/>
     <col min="20" max="20" width="5.44140625" style="1" customWidth="1"/>
     <col min="21" max="21" width="8.77734375" style="1" customWidth="1"/>
     <col min="22" max="23" width="8.33203125" style="1" customWidth="1"/>
     <col min="24" max="24" width="8.88671875" style="1"/>
-    <col min="25" max="25" width="14" style="64" customWidth="1"/>
+    <col min="25" max="25" width="14" style="71" customWidth="1"/>
     <col min="26" max="26" width="6.77734375" style="1" customWidth="1"/>
     <col min="27" max="27" width="7" style="1" customWidth="1"/>
     <col min="28" max="16384" width="8.88671875" style="1"/>
@@ -2000,15 +2662,15 @@
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="G1" s="12"/>
-      <c r="H1" s="70"/>
+      <c r="H1" s="82"/>
       <c r="I1" s="13"/>
       <c r="J1" s="14"/>
       <c r="K1" s="15"/>
       <c r="L1" s="12"/>
       <c r="M1" s="16"/>
-      <c r="N1" s="110"/>
+      <c r="N1" s="134"/>
       <c r="O1" s="12"/>
-      <c r="P1" s="116"/>
+      <c r="P1" s="140"/>
       <c r="Q1" s="9"/>
       <c r="R1" s="17"/>
       <c r="S1" s="17"/>
@@ -2021,25 +2683,25 @@
       <c r="Z1" s="17"/>
     </row>
     <row r="2" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A2" s="122"/>
+      <c r="A2" s="146"/>
       <c r="B2" s="18"/>
       <c r="C2" s="20"/>
       <c r="D2" s="21"/>
       <c r="E2" s="22"/>
-      <c r="F2" s="139" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="139"/>
-      <c r="J2" s="139"/>
-      <c r="K2" s="139"/>
-      <c r="L2" s="139"/>
-      <c r="M2" s="139"/>
-      <c r="N2" s="111"/>
+      <c r="F2" s="163" t="s">
+        <v>271</v>
+      </c>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
+      <c r="L2" s="163"/>
+      <c r="M2" s="163"/>
+      <c r="N2" s="135"/>
       <c r="O2" s="23"/>
-      <c r="P2" s="117"/>
-      <c r="Q2" s="102"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="126"/>
       <c r="R2" s="24"/>
       <c r="S2" s="24"/>
       <c r="T2" s="24"/>
@@ -2047,43 +2709,43 @@
       <c r="V2" s="25"/>
       <c r="W2" s="25"/>
       <c r="X2" s="25"/>
-      <c r="Y2" s="67"/>
+      <c r="Y2" s="75"/>
       <c r="Z2" s="25"/>
     </row>
     <row r="3" spans="1:27" ht="18.75" customHeight="1" thickBot="1">
       <c r="A3" s="18"/>
-      <c r="B3" s="135" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="136"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139"/>
-      <c r="N3" s="111"/>
-      <c r="O3" s="84" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q3" s="85">
+      <c r="B3" s="159" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" s="160"/>
+      <c r="D3" s="161"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
+      <c r="L3" s="163"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="135"/>
+      <c r="O3" s="99" t="s">
+        <v>86</v>
+      </c>
+      <c r="P3" s="142" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q3" s="100">
         <v>44166</v>
       </c>
-      <c r="R3" s="66"/>
+      <c r="R3" s="74"/>
       <c r="S3" s="24"/>
       <c r="T3" s="24"/>
       <c r="U3" s="25"/>
       <c r="V3" s="25"/>
       <c r="W3" s="25"/>
       <c r="X3" s="25"/>
-      <c r="Y3" s="67"/>
+      <c r="Y3" s="75"/>
       <c r="Z3" s="25"/>
     </row>
     <row r="4" spans="1:27">
@@ -2102,7 +2764,7 @@
       <c r="M4" s="32"/>
       <c r="N4" s="27"/>
       <c r="O4" s="28"/>
-      <c r="P4" s="119"/>
+      <c r="P4" s="143"/>
       <c r="Q4" s="28"/>
       <c r="R4" s="24"/>
       <c r="S4" s="24"/>
@@ -2111,7 +2773,7 @@
       <c r="V4" s="25"/>
       <c r="W4" s="25"/>
       <c r="X4" s="25"/>
-      <c r="Y4" s="67"/>
+      <c r="Y4" s="75"/>
       <c r="Z4" s="25"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1">
@@ -2120,19 +2782,19 @@
       <c r="C5" s="20"/>
       <c r="D5" s="21"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="G5" s="74"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="77"/>
+      <c r="F5" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="89"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="92"/>
       <c r="K5" s="26"/>
       <c r="L5" s="28"/>
       <c r="M5" s="32"/>
       <c r="N5" s="27"/>
       <c r="O5" s="28"/>
-      <c r="P5" s="119"/>
+      <c r="P5" s="143"/>
       <c r="Q5" s="28"/>
       <c r="R5" s="24"/>
       <c r="S5" s="24"/>
@@ -2141,30 +2803,30 @@
       <c r="V5" s="25"/>
       <c r="W5" s="25"/>
       <c r="X5" s="25"/>
-      <c r="Y5" s="67"/>
+      <c r="Y5" s="75"/>
       <c r="Z5" s="25"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1">
       <c r="A6" s="18"/>
-      <c r="B6" s="140" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="140"/>
-      <c r="D6" s="140"/>
+      <c r="B6" s="164" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="164"/>
+      <c r="D6" s="164"/>
       <c r="E6" s="22"/>
-      <c r="F6" s="78" t="s">
+      <c r="F6" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="79"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="82"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="97"/>
       <c r="K6" s="26"/>
       <c r="L6" s="28"/>
       <c r="M6" s="32"/>
       <c r="N6" s="27"/>
       <c r="O6" s="28"/>
-      <c r="P6" s="119"/>
+      <c r="P6" s="143"/>
       <c r="Q6" s="28"/>
       <c r="R6" s="24"/>
       <c r="S6" s="24"/>
@@ -2173,28 +2835,28 @@
       <c r="V6" s="25"/>
       <c r="W6" s="25"/>
       <c r="X6" s="25"/>
-      <c r="Y6" s="67"/>
+      <c r="Y6" s="75"/>
       <c r="Z6" s="25"/>
     </row>
     <row r="7" spans="1:27">
       <c r="A7" s="18"/>
-      <c r="B7" s="123"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="125"/>
+      <c r="B7" s="147"/>
+      <c r="C7" s="148"/>
+      <c r="D7" s="149"/>
       <c r="E7" s="22"/>
-      <c r="F7" s="83" t="s">
+      <c r="F7" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="79"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="82"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
       <c r="K7" s="26"/>
       <c r="L7" s="28"/>
       <c r="M7" s="32"/>
       <c r="N7" s="27"/>
       <c r="O7" s="28"/>
-      <c r="P7" s="119"/>
+      <c r="P7" s="143"/>
       <c r="Q7" s="28"/>
       <c r="R7" s="24"/>
       <c r="S7" s="24"/>
@@ -2203,7 +2865,7 @@
       <c r="V7" s="25"/>
       <c r="W7" s="25"/>
       <c r="X7" s="25"/>
-      <c r="Y7" s="67"/>
+      <c r="Y7" s="75"/>
       <c r="Z7" s="25"/>
     </row>
     <row r="8" spans="1:27">
@@ -2214,16 +2876,16 @@
       <c r="E8" s="22"/>
       <c r="F8" s="33"/>
       <c r="G8" s="18"/>
-      <c r="H8" s="71"/>
+      <c r="H8" s="83"/>
       <c r="I8" s="34"/>
       <c r="J8" s="35"/>
       <c r="K8" s="36"/>
       <c r="L8" s="37"/>
       <c r="M8" s="38"/>
-      <c r="N8" s="112"/>
+      <c r="N8" s="136"/>
       <c r="O8" s="39"/>
-      <c r="P8" s="117"/>
-      <c r="Q8" s="102"/>
+      <c r="P8" s="141"/>
+      <c r="Q8" s="126"/>
       <c r="R8" s="24"/>
       <c r="S8" s="24"/>
       <c r="T8" s="24"/>
@@ -2231,161 +2893,161 @@
       <c r="V8" s="25"/>
       <c r="W8" s="25"/>
       <c r="X8" s="25"/>
-      <c r="Y8" s="67"/>
+      <c r="Y8" s="75"/>
       <c r="Z8" s="25"/>
     </row>
-    <row r="9" spans="1:27" s="108" customFormat="1" ht="15" customHeight="1">
-      <c r="A9" s="94" t="s">
+    <row r="9" spans="1:27" s="132" customFormat="1" ht="15" customHeight="1">
+      <c r="A9" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="94" t="s">
+      <c r="C9" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="95" t="s">
+      <c r="D9" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="95" t="s">
+      <c r="E9" s="119" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="94" t="s">
+      <c r="F9" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="96" t="s">
+      <c r="G9" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="97" t="s">
+      <c r="H9" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="I9" s="98" t="s">
+      <c r="I9" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="99" t="s">
+      <c r="J9" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="100" t="s">
+      <c r="K9" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="L9" s="96" t="s">
+      <c r="L9" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="M9" s="98" t="s">
+      <c r="M9" s="122" t="s">
         <v>15</v>
       </c>
-      <c r="N9" s="113" t="s">
+      <c r="N9" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="101" t="s">
+      <c r="O9" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="92" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q9" s="69" t="s">
+      <c r="P9" s="116" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q9" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="R9" s="93" t="s">
-        <v>52</v>
-      </c>
-      <c r="S9" s="69" t="s">
-        <v>53</v>
-      </c>
-      <c r="T9" s="69" t="s">
-        <v>54</v>
-      </c>
-      <c r="U9" s="69" t="s">
+      <c r="R9" s="117" t="s">
+        <v>88</v>
+      </c>
+      <c r="S9" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="T9" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="U9" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="V9" s="69" t="s">
-        <v>55</v>
-      </c>
-      <c r="W9" s="69" t="s">
-        <v>56</v>
-      </c>
-      <c r="X9" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y9" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z9" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA9" s="69" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" s="134" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A10" s="109">
+      <c r="V9" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="W9" s="77" t="s">
+        <v>92</v>
+      </c>
+      <c r="X9" s="77" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y9" s="77" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z9" s="77" t="s">
+        <v>231</v>
+      </c>
+      <c r="AA9" s="77" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" s="158" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A10" s="133">
         <v>1</v>
       </c>
-      <c r="B10" s="126" t="s">
+      <c r="B10" s="150" t="s">
+        <v>261</v>
+      </c>
+      <c r="C10" s="151" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="127" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="127" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" s="127" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="128" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" s="109"/>
-      <c r="H10" s="129">
+      <c r="D10" s="151" t="s">
+        <v>269</v>
+      </c>
+      <c r="E10" s="151" t="s">
+        <v>262</v>
+      </c>
+      <c r="F10" s="152" t="s">
+        <v>200</v>
+      </c>
+      <c r="G10" s="133"/>
+      <c r="H10" s="153">
         <f t="shared" ref="H10" si="0">G10*N10</f>
         <v>0</v>
       </c>
-      <c r="I10" s="130"/>
-      <c r="J10" s="130"/>
-      <c r="K10" s="130"/>
-      <c r="L10" s="109"/>
-      <c r="M10" s="109"/>
-      <c r="N10" s="131">
+      <c r="I10" s="154"/>
+      <c r="J10" s="154"/>
+      <c r="K10" s="154"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="133"/>
+      <c r="N10" s="155">
         <v>18328</v>
       </c>
-      <c r="O10" s="132" t="s">
+      <c r="O10" s="156" t="s">
+        <v>193</v>
+      </c>
+      <c r="P10" s="155">
+        <v>513184</v>
+      </c>
+      <c r="Q10" s="152" t="s">
+        <v>263</v>
+      </c>
+      <c r="R10" s="157" t="s">
+        <v>264</v>
+      </c>
+      <c r="S10" s="157" t="s">
+        <v>30</v>
+      </c>
+      <c r="T10" s="152" t="s">
         <v>63</v>
       </c>
-      <c r="P10" s="131">
-        <v>513184</v>
-      </c>
-      <c r="Q10" s="128" t="s">
-        <v>73</v>
-      </c>
-      <c r="R10" s="133" t="s">
-        <v>74</v>
-      </c>
-      <c r="S10" s="133" t="s">
-        <v>29</v>
-      </c>
-      <c r="T10" s="128" t="s">
-        <v>37</v>
-      </c>
-      <c r="U10" s="133" t="s">
-        <v>66</v>
-      </c>
-      <c r="V10" s="133" t="s">
-        <v>30</v>
-      </c>
-      <c r="W10" s="133" t="s">
+      <c r="U10" s="157" t="s">
+        <v>225</v>
+      </c>
+      <c r="V10" s="157" t="s">
         <v>31</v>
       </c>
-      <c r="X10" s="133" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y10" s="128" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z10" s="133" t="s">
+      <c r="W10" s="157" t="s">
         <v>32</v>
       </c>
-      <c r="AA10" s="133">
+      <c r="X10" s="157" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y10" s="152" t="s">
+        <v>266</v>
+      </c>
+      <c r="Z10" s="157" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA10" s="157">
         <v>18328</v>
       </c>
     </row>
@@ -2411,7 +3073,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <tabColor indexed="11"/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z33"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.109375" customWidth="1"/>
@@ -2426,9 +3088,9 @@
     <col min="10" max="10" width="9.33203125" style="44" customWidth="1"/>
     <col min="11" max="11" width="10.109375" style="44" customWidth="1"/>
     <col min="12" max="13" width="0" style="44" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="16.33203125" style="64" customWidth="1"/>
-    <col min="16" max="16" width="10.21875" style="87" customWidth="1"/>
-    <col min="17" max="17" width="8.88671875" style="67"/>
+    <col min="15" max="15" width="16.33203125" style="71" customWidth="1"/>
+    <col min="16" max="16" width="10.21875" style="102" customWidth="1"/>
+    <col min="17" max="17" width="8.88671875" style="75"/>
     <col min="22" max="22" width="4.77734375" customWidth="1"/>
     <col min="23" max="23" width="4.33203125" customWidth="1"/>
   </cols>
@@ -2449,7 +3111,7 @@
       <c r="E1" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="91" t="s">
+      <c r="F1" s="115" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="40" t="s">
@@ -2476,13 +3138,13 @@
       <c r="N1" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="90" t="s">
+      <c r="O1" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="86" t="s">
+      <c r="P1" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" s="88" t="s">
+      <c r="Q1" s="103" t="s">
         <v>19</v>
       </c>
       <c r="R1" s="51" t="s">
@@ -2513,73 +3175,2212 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="107" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A2" s="109">
+    <row r="2" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A2" s="133">
         <v>1</v>
       </c>
-      <c r="B2" s="115" t="s">
+      <c r="B2" s="139" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="139" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="139" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="145"/>
+      <c r="H2" s="129">
+        <f>G2*N2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="139">
+        <v>312</v>
+      </c>
+      <c r="O2" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P2" s="139">
+        <v>9360</v>
+      </c>
+      <c r="Q2" s="76" t="s">
+        <v>114</v>
+      </c>
+      <c r="R2" s="109" t="s">
+        <v>246</v>
+      </c>
+      <c r="S2" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="U2" s="109" t="s">
+        <v>52</v>
+      </c>
+      <c r="V2" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W2" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y2" s="76" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z2" s="109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A3" s="133">
+        <v>2</v>
+      </c>
+      <c r="B3" s="139" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="139" t="s">
+        <v>235</v>
+      </c>
+      <c r="F3" s="139" t="s">
+        <v>196</v>
+      </c>
+      <c r="G3" s="145"/>
+      <c r="H3" s="129">
+        <f t="shared" ref="H3:H16" si="0">G3*N3</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="139">
+        <v>168</v>
+      </c>
+      <c r="O3" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P3" s="139">
+        <v>16800</v>
+      </c>
+      <c r="Q3" s="76" t="s">
+        <v>237</v>
+      </c>
+      <c r="R3" s="109" t="s">
+        <v>247</v>
+      </c>
+      <c r="S3" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="U3" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="V3" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W3" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X3" s="109" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y3" s="76" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z3" s="109" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A4" s="133">
+        <v>3</v>
+      </c>
+      <c r="B4" s="139" t="s">
+        <v>233</v>
+      </c>
+      <c r="C4" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="139" t="s">
+        <v>235</v>
+      </c>
+      <c r="F4" s="139" t="s">
+        <v>195</v>
+      </c>
+      <c r="G4" s="145"/>
+      <c r="H4" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="128"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="127"/>
+      <c r="M4" s="127"/>
+      <c r="N4" s="139">
+        <v>168</v>
+      </c>
+      <c r="O4" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P4" s="139">
+        <v>5040</v>
+      </c>
+      <c r="Q4" s="76" t="s">
+        <v>237</v>
+      </c>
+      <c r="R4" s="109" t="s">
+        <v>248</v>
+      </c>
+      <c r="S4" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T4" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="U4" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="V4" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W4" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X4" s="109" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y4" s="76" t="s">
+        <v>239</v>
+      </c>
+      <c r="Z4" s="109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A5" s="133">
+        <v>4</v>
+      </c>
+      <c r="B5" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="139" t="s">
+        <v>226</v>
+      </c>
+      <c r="F5" s="139" t="s">
+        <v>198</v>
+      </c>
+      <c r="G5" s="145"/>
+      <c r="H5" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="127"/>
+      <c r="M5" s="127"/>
+      <c r="N5" s="139">
+        <v>88</v>
+      </c>
+      <c r="O5" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P5" s="139">
+        <v>26400</v>
+      </c>
+      <c r="Q5" s="76" t="s">
+        <v>164</v>
+      </c>
+      <c r="R5" s="109" t="s">
+        <v>249</v>
+      </c>
+      <c r="S5" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T5" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="U5" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="V5" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W5" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X5" s="109" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y5" s="76" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z5" s="109" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A6" s="133">
+        <v>5</v>
+      </c>
+      <c r="B6" s="139" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="139" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" s="139" t="s">
+        <v>197</v>
+      </c>
+      <c r="G6" s="145"/>
+      <c r="H6" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="128"/>
+      <c r="J6" s="128"/>
+      <c r="K6" s="128"/>
+      <c r="L6" s="127"/>
+      <c r="M6" s="127"/>
+      <c r="N6" s="139">
+        <v>58</v>
+      </c>
+      <c r="O6" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P6" s="139">
+        <v>29000</v>
+      </c>
+      <c r="Q6" s="76" t="s">
+        <v>206</v>
+      </c>
+      <c r="R6" s="109" t="s">
+        <v>228</v>
+      </c>
+      <c r="S6" s="109" t="s">
+        <v>38</v>
+      </c>
+      <c r="T6" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="U6" s="109" t="s">
+        <v>73</v>
+      </c>
+      <c r="V6" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W6" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X6" s="109" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y6" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z6" s="109" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A7" s="133">
+        <v>6</v>
+      </c>
+      <c r="B7" s="139" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="139" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="139" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="145"/>
+      <c r="H7" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="128"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="128"/>
+      <c r="L7" s="127"/>
+      <c r="M7" s="127"/>
+      <c r="N7" s="139">
+        <v>107</v>
+      </c>
+      <c r="O7" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P7" s="139">
+        <v>32100</v>
+      </c>
+      <c r="Q7" s="76" t="s">
+        <v>99</v>
+      </c>
+      <c r="R7" s="109" t="s">
+        <v>134</v>
+      </c>
+      <c r="S7" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T7" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="U7" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="V7" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W7" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X7" s="109" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y7" s="76" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z7" s="109" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A8" s="133">
+        <v>7</v>
+      </c>
+      <c r="B8" s="139" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="139" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="139" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="145"/>
+      <c r="H8" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="128"/>
+      <c r="L8" s="127"/>
+      <c r="M8" s="127"/>
+      <c r="N8" s="139">
+        <v>107</v>
+      </c>
+      <c r="O8" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P8" s="139">
+        <v>3210</v>
+      </c>
+      <c r="Q8" s="76" t="s">
+        <v>99</v>
+      </c>
+      <c r="R8" s="109" t="s">
+        <v>100</v>
+      </c>
+      <c r="S8" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T8" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="U8" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="V8" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W8" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X8" s="109" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y8" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z8" s="109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A9" s="133">
+        <v>8</v>
+      </c>
+      <c r="B9" s="139" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="139" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="139" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="145"/>
+      <c r="H9" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="128"/>
+      <c r="L9" s="127"/>
+      <c r="M9" s="127"/>
+      <c r="N9" s="139">
+        <v>162</v>
+      </c>
+      <c r="O9" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P9" s="139">
+        <v>48600</v>
+      </c>
+      <c r="Q9" s="76" t="s">
+        <v>109</v>
+      </c>
+      <c r="R9" s="109" t="s">
+        <v>137</v>
+      </c>
+      <c r="S9" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T9" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="U9" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="V9" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W9" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X9" s="109" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y9" s="76" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z9" s="109" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A10" s="133">
+        <v>9</v>
+      </c>
+      <c r="B10" s="139" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="139" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="139" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="145"/>
+      <c r="H10" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="127"/>
+      <c r="M10" s="127"/>
+      <c r="N10" s="139">
+        <v>162</v>
+      </c>
+      <c r="O10" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P10" s="139">
+        <v>4860</v>
+      </c>
+      <c r="Q10" s="76" t="s">
+        <v>109</v>
+      </c>
+      <c r="R10" s="109" t="s">
+        <v>110</v>
+      </c>
+      <c r="S10" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T10" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="U10" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="V10" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W10" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X10" s="109" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y10" s="76" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z10" s="109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A11" s="133">
+        <v>10</v>
+      </c>
+      <c r="B11" s="139" t="s">
+        <v>234</v>
+      </c>
+      <c r="C11" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="139" t="s">
+        <v>236</v>
+      </c>
+      <c r="F11" s="139" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="145"/>
+      <c r="H11" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="127"/>
+      <c r="N11" s="139">
+        <v>115</v>
+      </c>
+      <c r="O11" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P11" s="139">
+        <v>34500</v>
+      </c>
+      <c r="Q11" s="76" t="s">
+        <v>240</v>
+      </c>
+      <c r="R11" s="109" t="s">
+        <v>241</v>
+      </c>
+      <c r="S11" s="109" t="s">
+        <v>38</v>
+      </c>
+      <c r="T11" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="U11" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="V11" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W11" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X11" s="109" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y11" s="76" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z11" s="109" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A12" s="133">
+        <v>11</v>
+      </c>
+      <c r="B12" s="139" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="139" t="s">
+        <v>236</v>
+      </c>
+      <c r="F12" s="139" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="145"/>
+      <c r="H12" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="128"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="128"/>
+      <c r="L12" s="127"/>
+      <c r="M12" s="127"/>
+      <c r="N12" s="139">
+        <v>115</v>
+      </c>
+      <c r="O12" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P12" s="139">
+        <v>3450</v>
+      </c>
+      <c r="Q12" s="76" t="s">
+        <v>240</v>
+      </c>
+      <c r="R12" s="109" t="s">
+        <v>244</v>
+      </c>
+      <c r="S12" s="109" t="s">
+        <v>38</v>
+      </c>
+      <c r="T12" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="U12" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="V12" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W12" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X12" s="109" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y12" s="76" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z12" s="109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A13" s="133">
+        <v>12</v>
+      </c>
+      <c r="B13" s="139" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="139" t="s">
+        <v>252</v>
+      </c>
+      <c r="F13" s="139" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="145"/>
+      <c r="H13" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="128"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="128"/>
+      <c r="L13" s="127"/>
+      <c r="M13" s="127"/>
+      <c r="N13" s="139">
+        <v>1000</v>
+      </c>
+      <c r="O13" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P13" s="139">
+        <v>30000</v>
+      </c>
+      <c r="Q13" s="76" t="s">
+        <v>255</v>
+      </c>
+      <c r="R13" s="109" t="s">
+        <v>256</v>
+      </c>
+      <c r="S13" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T13" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="U13" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="V13" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W13" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X13" s="109" t="s">
+        <v>223</v>
+      </c>
+      <c r="Y13" s="76" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z13" s="109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A14" s="133">
+        <v>13</v>
+      </c>
+      <c r="B14" s="139" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="139" t="s">
+        <v>253</v>
+      </c>
+      <c r="F14" s="139" t="s">
+        <v>195</v>
+      </c>
+      <c r="G14" s="145"/>
+      <c r="H14" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="128"/>
+      <c r="J14" s="128"/>
+      <c r="K14" s="128"/>
+      <c r="L14" s="127"/>
+      <c r="M14" s="127"/>
+      <c r="N14" s="139">
+        <v>3424</v>
+      </c>
+      <c r="O14" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P14" s="139">
+        <v>102720</v>
+      </c>
+      <c r="Q14" s="76" t="s">
+        <v>146</v>
+      </c>
+      <c r="R14" s="109" t="s">
+        <v>147</v>
+      </c>
+      <c r="S14" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T14" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="U14" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="V14" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W14" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X14" s="109" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y14" s="76" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z14" s="109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A15" s="133">
+        <v>14</v>
+      </c>
+      <c r="B15" s="139" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="139" t="s">
+        <v>254</v>
+      </c>
+      <c r="F15" s="139" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="145"/>
+      <c r="H15" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="128"/>
+      <c r="J15" s="128"/>
+      <c r="K15" s="128"/>
+      <c r="L15" s="127"/>
+      <c r="M15" s="127"/>
+      <c r="N15" s="139">
+        <v>675</v>
+      </c>
+      <c r="O15" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P15" s="139">
+        <v>20250</v>
+      </c>
+      <c r="Q15" s="76" t="s">
+        <v>258</v>
+      </c>
+      <c r="R15" s="109" t="s">
+        <v>259</v>
+      </c>
+      <c r="S15" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T15" s="76" t="s">
+        <v>43</v>
+      </c>
+      <c r="U15" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="V15" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W15" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X15" s="109" t="s">
+        <v>224</v>
+      </c>
+      <c r="Y15" s="76" t="s">
+        <v>260</v>
+      </c>
+      <c r="Z15" s="109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" s="131" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A16" s="133">
+        <v>15</v>
+      </c>
+      <c r="B16" s="139" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="139" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="139" t="s">
+        <v>168</v>
+      </c>
+      <c r="F16" s="139" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="145"/>
+      <c r="H16" s="129">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="128"/>
+      <c r="J16" s="128"/>
+      <c r="K16" s="128"/>
+      <c r="L16" s="127"/>
+      <c r="M16" s="127"/>
+      <c r="N16" s="139">
+        <v>180</v>
+      </c>
+      <c r="O16" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="P16" s="139">
+        <v>5400</v>
+      </c>
+      <c r="Q16" s="76" t="s">
+        <v>169</v>
+      </c>
+      <c r="R16" s="109" t="s">
+        <v>170</v>
+      </c>
+      <c r="S16" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T16" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="U16" s="109" t="s">
+        <v>57</v>
+      </c>
+      <c r="V16" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W16" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="X16" s="109" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y16" s="76" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z16" s="109" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" s="108" customFormat="1" ht="12">
+      <c r="A17" s="133">
+        <v>16</v>
+      </c>
+      <c r="B17" s="76" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="104" t="s">
+        <v>149</v>
+      </c>
+      <c r="F17" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="107"/>
+      <c r="H17" s="113">
+        <f t="shared" ref="H17:H26" si="1">G17*N17</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="106"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="104"/>
+      <c r="L17" s="104"/>
+      <c r="M17" s="106"/>
+      <c r="N17" s="107">
+        <v>488</v>
+      </c>
+      <c r="O17" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="P17" s="105">
+        <v>14640</v>
+      </c>
+      <c r="Q17" s="104" t="s">
+        <v>150</v>
+      </c>
+      <c r="R17" s="85" t="s">
+        <v>154</v>
+      </c>
+      <c r="S17" s="104" t="s">
+        <v>30</v>
+      </c>
+      <c r="T17" s="104" t="s">
+        <v>43</v>
+      </c>
+      <c r="U17" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="V17" s="104" t="s">
+        <v>31</v>
+      </c>
+      <c r="W17" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="X17" s="104" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y17" s="104" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z17" s="104" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" s="108" customFormat="1" ht="12">
+      <c r="A18" s="133">
+        <v>17</v>
+      </c>
+      <c r="B18" s="76" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="104" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="107"/>
+      <c r="H18" s="113">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="106"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="106"/>
+      <c r="N18" s="107">
+        <v>488</v>
+      </c>
+      <c r="O18" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="P18" s="105">
+        <v>146400</v>
+      </c>
+      <c r="Q18" s="104" t="s">
+        <v>150</v>
+      </c>
+      <c r="R18" s="85" t="s">
+        <v>151</v>
+      </c>
+      <c r="S18" s="104" t="s">
+        <v>30</v>
+      </c>
+      <c r="T18" s="104" t="s">
+        <v>43</v>
+      </c>
+      <c r="U18" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="V18" s="104" t="s">
+        <v>31</v>
+      </c>
+      <c r="W18" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="X18" s="104" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y18" s="104" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z18" s="104" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" s="108" customFormat="1" ht="12">
+      <c r="A19" s="133">
+        <v>18</v>
+      </c>
+      <c r="B19" s="76" t="s">
+        <v>172</v>
+      </c>
+      <c r="C19" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="104" t="s">
+        <v>173</v>
+      </c>
+      <c r="F19" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="107"/>
+      <c r="H19" s="113">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="106"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="104"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="106"/>
+      <c r="N19" s="107">
+        <v>488</v>
+      </c>
+      <c r="O19" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="P19" s="105">
+        <v>14640</v>
+      </c>
+      <c r="Q19" s="104" t="s">
+        <v>174</v>
+      </c>
+      <c r="R19" s="85" t="s">
+        <v>175</v>
+      </c>
+      <c r="S19" s="104" t="s">
+        <v>30</v>
+      </c>
+      <c r="T19" s="104" t="s">
+        <v>43</v>
+      </c>
+      <c r="U19" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="V19" s="104" t="s">
+        <v>31</v>
+      </c>
+      <c r="W19" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="X19" s="104" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y19" s="104" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z19" s="104" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" s="108" customFormat="1" ht="12">
+      <c r="A20" s="133">
+        <v>19</v>
+      </c>
+      <c r="B20" s="76" t="s">
+        <v>177</v>
+      </c>
+      <c r="C20" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="104" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="107"/>
+      <c r="H20" s="113">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="106"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="106"/>
+      <c r="N20" s="107">
+        <v>125</v>
+      </c>
+      <c r="O20" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="P20" s="105">
+        <v>75000</v>
+      </c>
+      <c r="Q20" s="104" t="s">
+        <v>179</v>
+      </c>
+      <c r="R20" s="85" t="s">
+        <v>180</v>
+      </c>
+      <c r="S20" s="104" t="s">
+        <v>30</v>
+      </c>
+      <c r="T20" s="104" t="s">
+        <v>43</v>
+      </c>
+      <c r="U20" s="104" t="s">
+        <v>47</v>
+      </c>
+      <c r="V20" s="104" t="s">
+        <v>31</v>
+      </c>
+      <c r="W20" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="X20" s="104" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y20" s="104" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z20" s="104" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" s="108" customFormat="1" ht="12">
+      <c r="A21" s="133">
+        <v>20</v>
+      </c>
+      <c r="B21" s="76" t="s">
+        <v>204</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="109" t="s">
+        <v>205</v>
+      </c>
+      <c r="F21" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="107"/>
+      <c r="H21" s="113">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="106"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="104"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="106"/>
+      <c r="N21" s="107">
+        <v>125</v>
+      </c>
+      <c r="O21" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="P21" s="105">
+        <v>3750</v>
+      </c>
+      <c r="Q21" s="110" t="s">
+        <v>179</v>
+      </c>
+      <c r="R21" s="111" t="s">
+        <v>213</v>
+      </c>
+      <c r="S21" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T21" s="109" t="s">
+        <v>43</v>
+      </c>
+      <c r="U21" s="112" t="s">
+        <v>47</v>
+      </c>
+      <c r="V21" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W21" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="X21" s="104" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y21" s="104" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z21" s="104" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" s="108" customFormat="1" ht="12">
+      <c r="A22" s="133">
+        <v>21</v>
+      </c>
+      <c r="B22" s="76" t="s">
+        <v>203</v>
+      </c>
+      <c r="C22" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="109" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" s="109" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="107"/>
+      <c r="H22" s="113">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="106"/>
+      <c r="J22" s="104"/>
+      <c r="K22" s="104"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="106"/>
+      <c r="N22" s="107">
+        <v>1050</v>
+      </c>
+      <c r="O22" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="P22" s="105">
+        <v>105000</v>
+      </c>
+      <c r="Q22" s="110" t="s">
+        <v>208</v>
+      </c>
+      <c r="R22" s="111" t="s">
+        <v>211</v>
+      </c>
+      <c r="S22" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T22" s="109" t="s">
+        <v>63</v>
+      </c>
+      <c r="U22" s="112" t="s">
+        <v>55</v>
+      </c>
+      <c r="V22" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W22" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="X22" s="104" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y22" s="104" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z22" s="104" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" s="108" customFormat="1" ht="12">
+      <c r="A23" s="133">
+        <v>22</v>
+      </c>
+      <c r="B23" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="C23" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="109" t="s">
+        <v>202</v>
+      </c>
+      <c r="F23" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="107"/>
+      <c r="H23" s="113">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="106"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="106"/>
+      <c r="N23" s="107">
+        <v>1050</v>
+      </c>
+      <c r="O23" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="P23" s="105">
+        <v>31500</v>
+      </c>
+      <c r="Q23" s="110" t="s">
+        <v>208</v>
+      </c>
+      <c r="R23" s="111" t="s">
+        <v>209</v>
+      </c>
+      <c r="S23" s="109" t="s">
+        <v>30</v>
+      </c>
+      <c r="T23" s="109" t="s">
+        <v>63</v>
+      </c>
+      <c r="U23" s="112" t="s">
+        <v>55</v>
+      </c>
+      <c r="V23" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="W23" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="X23" s="104" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y23" s="104" t="s">
+        <v>210</v>
+      </c>
+      <c r="Z23" s="104" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" s="108" customFormat="1" ht="12">
+      <c r="A24" s="133">
+        <v>23</v>
+      </c>
+      <c r="B24" s="76" t="s">
+        <v>182</v>
+      </c>
+      <c r="C24" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="104" t="s">
+        <v>183</v>
+      </c>
+      <c r="F24" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="107"/>
+      <c r="H24" s="113">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="106"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="106"/>
+      <c r="N24" s="107">
+        <v>124</v>
+      </c>
+      <c r="O24" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="P24" s="105">
+        <v>37200</v>
+      </c>
+      <c r="Q24" s="104" t="s">
+        <v>184</v>
+      </c>
+      <c r="R24" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="S24" s="104" t="s">
+        <v>30</v>
+      </c>
+      <c r="T24" s="104" t="s">
+        <v>43</v>
+      </c>
+      <c r="U24" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="V24" s="104" t="s">
+        <v>31</v>
+      </c>
+      <c r="W24" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="X24" s="104" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y24" s="104" t="s">
+        <v>186</v>
+      </c>
+      <c r="Z24" s="104" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" s="108" customFormat="1" ht="12">
+      <c r="A25" s="133">
+        <v>24</v>
+      </c>
+      <c r="B25" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="104" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="107"/>
+      <c r="H25" s="113">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="106"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="104"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="106"/>
+      <c r="N25" s="107">
+        <v>188</v>
+      </c>
+      <c r="O25" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="P25" s="105">
+        <v>5640</v>
+      </c>
+      <c r="Q25" s="104" t="s">
+        <v>104</v>
+      </c>
+      <c r="R25" s="85" t="s">
+        <v>105</v>
+      </c>
+      <c r="S25" s="104" t="s">
+        <v>30</v>
+      </c>
+      <c r="T25" s="104" t="s">
+        <v>43</v>
+      </c>
+      <c r="U25" s="104" t="s">
+        <v>47</v>
+      </c>
+      <c r="V25" s="104" t="s">
+        <v>31</v>
+      </c>
+      <c r="W25" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="X25" s="104" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y25" s="104" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z25" s="104" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" s="108" customFormat="1" ht="12">
+      <c r="A26" s="133">
+        <v>25</v>
+      </c>
+      <c r="B26" s="76" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" s="104" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="E26" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="109" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="107"/>
+      <c r="H26" s="113">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="106"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="104"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="106"/>
+      <c r="N26" s="107">
+        <v>188</v>
+      </c>
+      <c r="O26" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="P26" s="105">
+        <v>94000</v>
+      </c>
+      <c r="Q26" s="104" t="s">
+        <v>104</v>
+      </c>
+      <c r="R26" s="85" t="s">
+        <v>140</v>
+      </c>
+      <c r="S26" s="104" t="s">
+        <v>30</v>
+      </c>
+      <c r="T26" s="104" t="s">
+        <v>43</v>
+      </c>
+      <c r="U26" s="104" t="s">
+        <v>47</v>
+      </c>
+      <c r="V26" s="104" t="s">
+        <v>31</v>
+      </c>
+      <c r="W26" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="X26" s="104" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y26" s="104" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z26" s="104" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" s="54" customFormat="1" ht="15" customHeight="1">
+      <c r="A27" s="133">
+        <v>26</v>
+      </c>
+      <c r="B27" s="86" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="85" t="s">
+        <v>117</v>
+      </c>
+      <c r="F27" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" s="79"/>
+      <c r="H27" s="78">
+        <f t="shared" ref="H27:H33" si="2">G27*N27</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="87"/>
+      <c r="J27" s="79"/>
+      <c r="K27" s="79"/>
+      <c r="L27" s="79"/>
+      <c r="M27" s="79"/>
+      <c r="N27" s="81">
+        <v>608</v>
+      </c>
+      <c r="O27" s="79" t="s">
+        <v>194</v>
+      </c>
+      <c r="P27" s="81">
+        <v>30</v>
+      </c>
+      <c r="Q27" s="79" t="s">
+        <v>118</v>
+      </c>
+      <c r="R27" s="80" t="s">
+        <v>119</v>
+      </c>
+      <c r="S27" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="T27" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="U27" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="V27" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="W27" s="80" t="s">
+        <v>32</v>
+      </c>
+      <c r="X27" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="115" t="s">
+      <c r="Y27" s="80" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z27" s="80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" s="54" customFormat="1" ht="15" customHeight="1">
+      <c r="A28" s="133">
+        <v>27</v>
+      </c>
+      <c r="B28" s="86" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="85" t="s">
+        <v>157</v>
+      </c>
+      <c r="F28" s="109" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="79"/>
+      <c r="H28" s="78">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="87"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="79"/>
+      <c r="L28" s="79"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="81">
+        <v>712</v>
+      </c>
+      <c r="O28" s="79" t="s">
+        <v>193</v>
+      </c>
+      <c r="P28" s="81">
+        <v>100</v>
+      </c>
+      <c r="Q28" s="79" t="s">
+        <v>158</v>
+      </c>
+      <c r="R28" s="80" t="s">
+        <v>159</v>
+      </c>
+      <c r="S28" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="T28" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="U28" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="115" t="s">
+      <c r="V28" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="W28" s="80" t="s">
+        <v>32</v>
+      </c>
+      <c r="X28" s="80" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y28" s="80" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z28" s="80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" s="54" customFormat="1" ht="15" customHeight="1">
+      <c r="A29" s="133">
+        <v>28</v>
+      </c>
+      <c r="B29" s="86" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="85" t="s">
+        <v>157</v>
+      </c>
+      <c r="F29" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" s="79"/>
+      <c r="H29" s="78">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="87"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="81">
+        <v>712</v>
+      </c>
+      <c r="O29" s="79" t="s">
+        <v>194</v>
+      </c>
+      <c r="P29" s="81">
+        <v>30</v>
+      </c>
+      <c r="Q29" s="79" t="s">
+        <v>158</v>
+      </c>
+      <c r="R29" s="80" t="s">
+        <v>161</v>
+      </c>
+      <c r="S29" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="T29" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="U29" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="115" t="s">
+      <c r="V29" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="W29" s="80" t="s">
+        <v>32</v>
+      </c>
+      <c r="X29" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="115" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="121"/>
-      <c r="H2" s="105">
-        <f>G2*N2</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="104"/>
-      <c r="J2" s="104"/>
-      <c r="K2" s="104"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="115">
-        <v>312</v>
-      </c>
-      <c r="O2" s="106" t="s">
-        <v>63</v>
-      </c>
-      <c r="P2" s="115">
-        <v>9360</v>
-      </c>
-      <c r="Q2" s="68" t="s">
+      <c r="Y29" s="80" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z29" s="80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" s="54" customFormat="1" ht="15" customHeight="1">
+      <c r="A30" s="133">
+        <v>29</v>
+      </c>
+      <c r="B30" s="86" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="85" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="79"/>
+      <c r="H30" s="78">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="87"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="81">
+        <v>115</v>
+      </c>
+      <c r="O30" s="79" t="s">
+        <v>193</v>
+      </c>
+      <c r="P30" s="81">
+        <v>300</v>
+      </c>
+      <c r="Q30" s="79" t="s">
+        <v>190</v>
+      </c>
+      <c r="R30" s="80" t="s">
+        <v>191</v>
+      </c>
+      <c r="S30" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="T30" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="U30" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="V30" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="W30" s="80" t="s">
+        <v>32</v>
+      </c>
+      <c r="X30" s="80" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y30" s="80" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z30" s="80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" s="54" customFormat="1" ht="15" customHeight="1">
+      <c r="A31" s="133">
+        <v>30</v>
+      </c>
+      <c r="B31" s="86" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="85" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" s="109" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="79"/>
+      <c r="H31" s="78">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="87"/>
+      <c r="J31" s="79"/>
+      <c r="K31" s="79"/>
+      <c r="L31" s="79"/>
+      <c r="M31" s="79"/>
+      <c r="N31" s="81">
+        <v>764</v>
+      </c>
+      <c r="O31" s="79" t="s">
+        <v>194</v>
+      </c>
+      <c r="P31" s="81">
+        <v>28</v>
+      </c>
+      <c r="Q31" s="79" t="s">
+        <v>123</v>
+      </c>
+      <c r="R31" s="80" t="s">
+        <v>124</v>
+      </c>
+      <c r="S31" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="T31" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="U31" s="80" t="s">
+        <v>39</v>
+      </c>
+      <c r="V31" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="W31" s="80" t="s">
+        <v>32</v>
+      </c>
+      <c r="X31" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y31" s="80" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z31" s="80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" s="54" customFormat="1" ht="15" customHeight="1">
+      <c r="A32" s="133">
+        <v>31</v>
+      </c>
+      <c r="B32" s="86" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" s="85" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="109" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" s="79"/>
+      <c r="H32" s="78">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="87"/>
+      <c r="J32" s="79"/>
+      <c r="K32" s="79"/>
+      <c r="L32" s="79"/>
+      <c r="M32" s="79"/>
+      <c r="N32" s="81">
+        <v>1078</v>
+      </c>
+      <c r="O32" s="79" t="s">
+        <v>194</v>
+      </c>
+      <c r="P32" s="81">
+        <v>28</v>
+      </c>
+      <c r="Q32" s="79" t="s">
+        <v>128</v>
+      </c>
+      <c r="R32" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="S32" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="T32" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="U32" s="80" t="s">
+        <v>39</v>
+      </c>
+      <c r="V32" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="W32" s="80" t="s">
+        <v>32</v>
+      </c>
+      <c r="X32" s="80" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y32" s="80" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z32" s="80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" s="54" customFormat="1" ht="15" customHeight="1">
+      <c r="A33" s="133">
+        <v>32</v>
+      </c>
+      <c r="B33" s="86" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="85" t="s">
+        <v>131</v>
+      </c>
+      <c r="F33" s="109" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" s="79"/>
+      <c r="H33" s="78">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="87"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
+      <c r="N33" s="81">
+        <v>1268</v>
+      </c>
+      <c r="O33" s="79" t="s">
+        <v>193</v>
+      </c>
+      <c r="P33" s="81">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="79" t="s">
+        <v>132</v>
+      </c>
+      <c r="R33" s="80" t="s">
+        <v>143</v>
+      </c>
+      <c r="S33" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="T33" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="U33" s="80" t="s">
+        <v>42</v>
+      </c>
+      <c r="V33" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="W33" s="80" t="s">
+        <v>32</v>
+      </c>
+      <c r="X33" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="R2" s="89" t="s">
-        <v>70</v>
-      </c>
-      <c r="S2" s="89" t="s">
-        <v>29</v>
-      </c>
-      <c r="T2" s="68" t="s">
-        <v>35</v>
-      </c>
-      <c r="U2" s="89" t="s">
-        <v>36</v>
-      </c>
-      <c r="V2" s="89" t="s">
-        <v>30</v>
-      </c>
-      <c r="W2" s="89" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" s="89" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y2" s="68" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z2" s="89" t="s">
-        <v>34</v>
+      <c r="Y33" s="80" t="s">
+        <v>144</v>
+      </c>
+      <c r="Z33" s="80">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +5397,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <tabColor indexed="11"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="7.33203125" style="19" customWidth="1"/>
@@ -2613,117 +5414,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.7" customHeight="1">
-      <c r="A1" s="141" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="141"/>
+      <c r="A1" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="165"/>
       <c r="C1" s="56" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="D1" s="57" t="str">
         <f>'시트2 32품목 스티커'!B2</f>
         <v>51320</v>
       </c>
-      <c r="G1" s="141" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="141"/>
+      <c r="G1" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="165"/>
       <c r="I1" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="57" t="e">
-        <f>'시트2 32품목 스티커'!#REF!</f>
-        <v>#REF!</v>
+        <v>76</v>
+      </c>
+      <c r="J1" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B10</f>
+        <v>51311</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.7" customHeight="1">
       <c r="A2" s="58" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B2" s="59" t="str">
         <f>'시트2 32품목 스티커'!E2</f>
         <v>암로다정</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="D2" s="60">
         <f>'시트2 32품목 스티커'!N2</f>
         <v>312</v>
       </c>
       <c r="G2" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="59" t="e">
-        <f>'시트2 32품목 스티커'!#REF!</f>
-        <v>#REF!</v>
+        <v>77</v>
+      </c>
+      <c r="H2" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E10</f>
+        <v>다노펜정</v>
       </c>
       <c r="I2" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="61" t="e">
-        <f>'시트2 32품목 스티커'!#REF!</f>
-        <v>#REF!</v>
+        <v>78</v>
+      </c>
+      <c r="J2" s="61">
+        <f>'시트2 32품목 스티커'!N10</f>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="13.7" customHeight="1">
       <c r="A3" s="58" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B3" s="59" t="str">
         <f>'시트2 32품목 스티커'!D2</f>
         <v>(유) 한풍제약</v>
       </c>
       <c r="C3" s="58" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D3" s="61">
         <f>'시트2 32품목 스티커'!H2</f>
         <v>0</v>
       </c>
       <c r="G3" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="59" t="e">
-        <f>'시트2 32품목 스티커'!#REF!</f>
-        <v>#REF!</v>
+        <v>79</v>
+      </c>
+      <c r="H3" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D10</f>
+        <v>(유) 한풍제약</v>
       </c>
       <c r="I3" s="58" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="62" t="e">
-        <f>'시트2 32품목 스티커'!#REF!</f>
-        <v>#REF!</v>
+        <v>80</v>
+      </c>
+      <c r="J3" s="62">
+        <f>'시트2 32품목 스티커'!H10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="13.7" customHeight="1">
       <c r="A4" s="58" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B4" s="59">
         <f>'시트2 32품목 스티커'!J2</f>
         <v>0</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="D4" s="61">
         <f>'시트2 32품목 스티커'!K2</f>
         <v>0</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="59" t="e">
-        <f>'시트2 32품목 스티커'!#REF!</f>
-        <v>#REF!</v>
+        <v>81</v>
+      </c>
+      <c r="H4" s="59">
+        <f>'시트2 32품목 스티커'!J10</f>
+        <v>0</v>
       </c>
       <c r="I4" s="58" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="61" t="e">
-        <f>'시트2 32품목 스티커'!#REF!</f>
-        <v>#REF!</v>
+        <v>82</v>
+      </c>
+      <c r="J4" s="61">
+        <f>'시트2 32품목 스티커'!K10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="13.7" customHeight="1">
@@ -2735,52 +5536,2536 @@
         <v>0</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D5" s="61"/>
       <c r="G5" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="63" t="e">
-        <f>'시트2 32품목 스티커'!#REF!</f>
-        <v>#REF!</v>
+      <c r="H5" s="63">
+        <f>'시트2 32품목 스티커'!I10</f>
+        <v>0</v>
       </c>
       <c r="I5" s="58" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="J5" s="61"/>
     </row>
     <row r="6" spans="1:10" ht="13.7" customHeight="1">
       <c r="A6" s="58" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B6" s="59">
         <f>'시트2 32품목 스티커'!G2</f>
         <v>0</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D6" s="61"/>
       <c r="G6" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="59" t="e">
-        <f>'시트2 32품목 스티커'!#REF!</f>
-        <v>#REF!</v>
+        <v>84</v>
+      </c>
+      <c r="H6" s="59">
+        <f>'시트2 32품목 스티커'!G10</f>
+        <v>0</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="J6" s="61"/>
     </row>
     <row r="7" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="8" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A8" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="165"/>
+      <c r="C8" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B3</f>
+        <v>58424</v>
+      </c>
+      <c r="G8" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="165"/>
+      <c r="I8" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B11</f>
+        <v>58474</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A9" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E3</f>
+        <v>가바페캅셀100mg/</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="62">
+        <f>'시트2 32품목 스티커'!N3</f>
+        <v>168</v>
+      </c>
+      <c r="G9" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E11</f>
+        <v>덱시네정 300mg</v>
+      </c>
+      <c r="I9" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="61">
+        <f>'시트2 32품목 스티커'!N11</f>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A10" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D3</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="61">
+        <f>'시트2 32품목 스티커'!H3</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D11</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I10" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="61">
+        <f>'시트2 32품목 스티커'!H11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A11" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="59">
+        <f>'시트2 32품목 스티커'!J3</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="61">
+        <f>'시트2 32품목 스티커'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="59">
+        <f>'시트2 32품목 스티커'!J11</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="61">
+        <f>'시트2 32품목 스티커'!K11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A12" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="63">
+        <f>'시트2 32품목 스티커'!I3</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="61"/>
+      <c r="G12" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="63">
+        <f>'시트2 32품목 스티커'!I11</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="61"/>
+    </row>
+    <row r="13" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A13" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="59">
+        <f>'시트2 32품목 스티커'!G3</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="61"/>
+      <c r="G13" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="59">
+        <f>'시트2 32품목 스티커'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J13" s="61"/>
+    </row>
+    <row r="14" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="15" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A15" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="165"/>
+      <c r="C15" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B4</f>
+        <v>58425</v>
+      </c>
+      <c r="G15" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" s="165"/>
+      <c r="I15" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B12</f>
+        <v>58516</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A16" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E4</f>
+        <v>가바페캅셀100mg/</v>
+      </c>
+      <c r="C16" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="62">
+        <f>'시트2 32품목 스티커'!N4</f>
+        <v>168</v>
+      </c>
+      <c r="G16" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E12</f>
+        <v>덱시네정 300mg</v>
+      </c>
+      <c r="I16" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J16" s="61">
+        <f>'시트2 32품목 스티커'!N12</f>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A17" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D4</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C17" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="61">
+        <f>'시트2 32품목 스티커'!H4</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H17" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D12</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I17" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" s="61">
+        <f>'시트2 32품목 스티커'!H12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A18" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="59">
+        <f>'시트2 32품목 스티커'!J4</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="61">
+        <f>'시트2 32품목 스티커'!K4</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="59">
+        <f>'시트2 32품목 스티커'!J12</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J18" s="61">
+        <f>'시트2 32품목 스티커'!K12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A19" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="63">
+        <f>'시트2 32품목 스티커'!I4</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="61"/>
+      <c r="G19" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="63">
+        <f>'시트2 32품목 스티커'!I12</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J19" s="61"/>
+    </row>
+    <row r="20" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A20" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="59">
+        <f>'시트2 32품목 스티커'!G4</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="61"/>
+      <c r="G20" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H20" s="59">
+        <f>'시트2 32품목 스티커'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J20" s="61"/>
+    </row>
+    <row r="21" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="22" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A22" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="165"/>
+      <c r="C22" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B5</f>
+        <v>53513</v>
+      </c>
+      <c r="G22" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="165"/>
+      <c r="I22" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B13</f>
+        <v>59297</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A23" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E5</f>
+        <v>가스모프정 5mg/</v>
+      </c>
+      <c r="C23" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="62">
+        <f>'시트2 32품목 스티커'!N5</f>
+        <v>88</v>
+      </c>
+      <c r="G23" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H23" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E13</f>
+        <v>도네일정 10mg</v>
+      </c>
+      <c r="I23" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J23" s="61">
+        <f>'시트2 32품목 스티커'!N13</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A24" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D5</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C24" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="61">
+        <f>'시트2 32품목 스티커'!H5</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H24" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D13</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I24" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J24" s="61">
+        <f>'시트2 32품목 스티커'!H13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A25" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="59">
+        <f>'시트2 32품목 스티커'!J5</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="61">
+        <f>'시트2 32품목 스티커'!K5</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="59">
+        <f>'시트2 32품목 스티커'!J13</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J25" s="61">
+        <f>'시트2 32품목 스티커'!K13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A26" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="63">
+        <f>'시트2 32품목 스티커'!I5</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="61"/>
+      <c r="G26" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="63">
+        <f>'시트2 32품목 스티커'!I13</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J26" s="61"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A27" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="59">
+        <f>'시트2 32품목 스티커'!G5</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="61"/>
+      <c r="G27" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="59">
+        <f>'시트2 32품목 스티커'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J27" s="61"/>
+    </row>
+    <row r="28" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="29" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A29" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="165"/>
+      <c r="C29" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B6</f>
+        <v>54440</v>
+      </c>
+      <c r="G29" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" s="165"/>
+      <c r="I29" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J29" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B14</f>
+        <v>52295</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A30" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E6</f>
+        <v>네로민정 10mg/</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="62">
+        <f>'시트2 32품목 스티커'!N6</f>
+        <v>58</v>
+      </c>
+      <c r="G30" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E14</f>
+        <v>도네일정 23mg/</v>
+      </c>
+      <c r="I30" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J30" s="61">
+        <f>'시트2 32품목 스티커'!N14</f>
+        <v>3424</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A31" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D6</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C31" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="61">
+        <f>'시트2 32품목 스티커'!H6</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H31" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D14</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I31" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J31" s="61">
+        <f>'시트2 32품목 스티커'!H14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A32" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="59">
+        <f>'시트2 32품목 스티커'!J6</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="61">
+        <f>'시트2 32품목 스티커'!K6</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H32" s="59">
+        <f>'시트2 32품목 스티커'!J14</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J32" s="61">
+        <f>'시트2 32품목 스티커'!K14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A33" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="63">
+        <f>'시트2 32품목 스티커'!I6</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="61"/>
+      <c r="G33" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="63">
+        <f>'시트2 32품목 스티커'!I14</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J33" s="61"/>
+    </row>
+    <row r="34" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A34" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="59">
+        <f>'시트2 32품목 스티커'!G6</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="61"/>
+      <c r="G34" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" s="59">
+        <f>'시트2 32품목 스티커'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J34" s="61"/>
+    </row>
+    <row r="35" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="36" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A36" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="165"/>
+      <c r="C36" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B7</f>
+        <v>51314</v>
+      </c>
+      <c r="G36" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H36" s="165"/>
+      <c r="I36" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J36" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B15</f>
+        <v>59296</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A37" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E7</f>
+        <v>다노펜세미정</v>
+      </c>
+      <c r="C37" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="62">
+        <f>'시트2 32품목 스티커'!N7</f>
+        <v>107</v>
+      </c>
+      <c r="G37" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H37" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E15</f>
+        <v>도네일정 5mg</v>
+      </c>
+      <c r="I37" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J37" s="61">
+        <f>'시트2 32품목 스티커'!N15</f>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A38" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D7</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C38" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="61">
+        <f>'시트2 32품목 스티커'!H7</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H38" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D15</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I38" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J38" s="61">
+        <f>'시트2 32품목 스티커'!H15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A39" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" s="59">
+        <f>'시트2 32품목 스티커'!J7</f>
+        <v>0</v>
+      </c>
+      <c r="C39" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="61">
+        <f>'시트2 32품목 스티커'!K7</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" s="59">
+        <f>'시트2 32품목 스티커'!J15</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J39" s="61">
+        <f>'시트2 32품목 스티커'!K15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A40" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="63">
+        <f>'시트2 32품목 스티커'!I7</f>
+        <v>0</v>
+      </c>
+      <c r="C40" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="61"/>
+      <c r="G40" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="63">
+        <f>'시트2 32품목 스티커'!I15</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J40" s="61"/>
+    </row>
+    <row r="41" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A41" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="59">
+        <f>'시트2 32품목 스티커'!G7</f>
+        <v>0</v>
+      </c>
+      <c r="C41" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" s="61"/>
+      <c r="G41" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H41" s="59">
+        <f>'시트2 32품목 스티커'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J41" s="61"/>
+    </row>
+    <row r="42" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="43" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A43" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B43" s="165"/>
+      <c r="C43" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B8</f>
+        <v>51313</v>
+      </c>
+      <c r="G43" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H43" s="165"/>
+      <c r="I43" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J43" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B16</f>
+        <v>53609</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A44" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E8</f>
+        <v>다노펜세미정</v>
+      </c>
+      <c r="C44" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" s="61">
+        <f>'시트2 32품목 스티커'!N8</f>
+        <v>107</v>
+      </c>
+      <c r="G44" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H44" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E16</f>
+        <v>디세나캅셀 50mg</v>
+      </c>
+      <c r="I44" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J44" s="61">
+        <f>'시트2 32품목 스티커'!N16</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A45" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D8</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C45" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" s="61">
+        <f>'시트2 32품목 스티커'!H8</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H45" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D16</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I45" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J45" s="61">
+        <f>'시트2 32품목 스티커'!H16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A46" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" s="59">
+        <f>'시트2 32품목 스티커'!J8</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46" s="61">
+        <f>'시트2 32품목 스티커'!K8</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H46" s="59">
+        <f>'시트2 32품목 스티커'!J16</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J46" s="61">
+        <f>'시트2 32품목 스티커'!K16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A47" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="63">
+        <f>'시트2 32품목 스티커'!I8</f>
+        <v>0</v>
+      </c>
+      <c r="C47" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" s="61"/>
+      <c r="G47" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="63">
+        <f>'시트2 32품목 스티커'!I16</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J47" s="61"/>
+    </row>
+    <row r="48" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A48" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="59">
+        <f>'시트2 32품목 스티커'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="C48" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" s="61"/>
+      <c r="G48" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H48" s="64">
+        <f>'시트2 32품목 스티커'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J48" s="61"/>
+    </row>
+    <row r="49" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="50" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A50" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" s="165"/>
+      <c r="C50" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B9</f>
+        <v>51312</v>
+      </c>
+      <c r="G50" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H50" s="165"/>
+      <c r="I50" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J50" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B17</f>
+        <v>52136</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A51" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B51" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E9</f>
+        <v>다노펜정</v>
+      </c>
+      <c r="C51" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D51" s="73">
+        <f>'시트2 32품목 스티커'!N9</f>
+        <v>162</v>
+      </c>
+      <c r="G51" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H51" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E17</f>
+        <v>로사탈정 50mg</v>
+      </c>
+      <c r="I51" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J51" s="61">
+        <f>'시트2 32품목 스티커'!N17</f>
+        <v>488</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A52" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D9</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C52" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" s="61">
+        <f>'시트2 32품목 스티커'!H9</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H52" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D17</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I52" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J52" s="61">
+        <f>'시트2 32품목 스티커'!H17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A53" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B53" s="59">
+        <f>'시트2 32품목 스티커'!J9</f>
+        <v>0</v>
+      </c>
+      <c r="C53" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53" s="61">
+        <f>'시트2 32품목 스티커'!K9</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H53" s="59">
+        <f>'시트2 32품목 스티커'!J17</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J53" s="61">
+        <f>'시트2 32품목 스티커'!K17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A54" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="63">
+        <f>'시트2 32품목 스티커'!I9</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D54" s="61"/>
+      <c r="G54" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54" s="63">
+        <f>'시트2 32품목 스티커'!I17</f>
+        <v>0</v>
+      </c>
+      <c r="I54" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J54" s="61"/>
+    </row>
+    <row r="55" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A55" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="59">
+        <f>'시트2 32품목 스티커'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="C55" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D55" s="61"/>
+      <c r="G55" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H55" s="59">
+        <f>'시트2 32품목 스티커'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J55" s="61"/>
+    </row>
+    <row r="56" spans="1:10" ht="7.5" customHeight="1">
+      <c r="A56" s="65"/>
+      <c r="B56" s="66"/>
+      <c r="C56" s="65"/>
+      <c r="D56" s="67"/>
+      <c r="G56" s="65"/>
+      <c r="H56" s="66"/>
+      <c r="I56" s="65"/>
+      <c r="J56" s="67"/>
+    </row>
+    <row r="57" spans="1:10" ht="7.5" customHeight="1"/>
+    <row r="58" spans="1:10" s="70" customFormat="1" ht="13.7" customHeight="1">
+      <c r="A58" s="166" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58" s="166"/>
+      <c r="C58" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58" s="69" t="str">
+        <f>'시트2 32품목 스티커'!B18</f>
+        <v>52137</v>
+      </c>
+      <c r="G58" s="166" t="s">
+        <v>75</v>
+      </c>
+      <c r="H58" s="166"/>
+      <c r="I58" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="J58" s="69" t="str">
+        <f>'시트2 32품목 스티커'!B26</f>
+        <v>51319</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A59" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E18</f>
+        <v>로사탈정 50mg</v>
+      </c>
+      <c r="C59" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D59" s="61">
+        <f>'시트2 32품목 스티커'!N18</f>
+        <v>488</v>
+      </c>
+      <c r="G59" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H59" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E26</f>
+        <v>아세네정</v>
+      </c>
+      <c r="I59" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J59" s="61">
+        <f>'시트2 32품목 스티커'!N26</f>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A60" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D18</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C60" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D60" s="62">
+        <f>'시트2 32품목 스티커'!H18</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H60" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D26</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I60" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J60" s="62">
+        <f>'시트2 32품목 스티커'!H26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A61" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" s="59">
+        <f>'시트2 32품목 스티커'!J18</f>
+        <v>0</v>
+      </c>
+      <c r="C61" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" s="61">
+        <f>'시트2 32품목 스티커'!K18</f>
+        <v>0</v>
+      </c>
+      <c r="G61" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H61" s="59">
+        <f>'시트2 32품목 스티커'!J26</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J61" s="61">
+        <f>'시트2 32품목 스티커'!K26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A62" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="63">
+        <f>'시트2 32품목 스티커'!I18</f>
+        <v>0</v>
+      </c>
+      <c r="C62" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D62" s="61"/>
+      <c r="G62" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="63">
+        <f>'시트2 32품목 스티커'!I26</f>
+        <v>0</v>
+      </c>
+      <c r="I62" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J62" s="61"/>
+    </row>
+    <row r="63" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A63" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" s="59">
+        <f>'시트2 32품목 스티커'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="C63" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" s="61"/>
+      <c r="G63" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H63" s="59">
+        <f>'시트2 32품목 스티커'!G26</f>
+        <v>0</v>
+      </c>
+      <c r="I63" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J63" s="61"/>
+    </row>
+    <row r="64" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="65" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A65" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B65" s="165"/>
+      <c r="C65" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D65" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B19</f>
+        <v>53518</v>
+      </c>
+      <c r="G65" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H65" s="165"/>
+      <c r="I65" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J65" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B27</f>
+        <v>51322</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A66" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B66" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E19</f>
+        <v>로사탈플러스정</v>
+      </c>
+      <c r="C66" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D66" s="61">
+        <f>'시트2 32품목 스티커'!N19</f>
+        <v>488</v>
+      </c>
+      <c r="G66" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H66" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E27</f>
+        <v>에이토바정 10mg</v>
+      </c>
+      <c r="I66" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J66" s="61">
+        <f>'시트2 32품목 스티커'!N27</f>
+        <v>608</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A67" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B67" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D19</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C67" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D67" s="62">
+        <f>'시트2 32품목 스티커'!H19</f>
+        <v>0</v>
+      </c>
+      <c r="G67" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H67" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D27</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I67" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J67" s="62">
+        <f>'시트2 32품목 스티커'!H27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A68" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68" s="59">
+        <f>'시트2 32품목 스티커'!J19</f>
+        <v>0</v>
+      </c>
+      <c r="C68" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D68" s="61">
+        <f>'시트2 32품목 스티커'!K19</f>
+        <v>0</v>
+      </c>
+      <c r="G68" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H68" s="59">
+        <f>'시트2 32품목 스티커'!J27</f>
+        <v>0</v>
+      </c>
+      <c r="I68" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J68" s="61">
+        <f>'시트2 32품목 스티커'!K27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A69" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" s="63">
+        <f>'시트2 32품목 스티커'!I19</f>
+        <v>0</v>
+      </c>
+      <c r="C69" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D69" s="61"/>
+      <c r="G69" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H69" s="63">
+        <f>'시트2 32품목 스티커'!I27</f>
+        <v>0</v>
+      </c>
+      <c r="I69" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J69" s="61"/>
+    </row>
+    <row r="70" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A70" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" s="59">
+        <f>'시트2 32품목 스티커'!G19</f>
+        <v>0</v>
+      </c>
+      <c r="C70" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D70" s="61"/>
+      <c r="G70" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H70" s="64">
+        <f>'시트2 32품목 스티커'!G27</f>
+        <v>0</v>
+      </c>
+      <c r="I70" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J70" s="61"/>
+    </row>
+    <row r="71" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="72" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A72" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" s="165"/>
+      <c r="C72" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D72" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B20</f>
+        <v>53519</v>
+      </c>
+      <c r="G72" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H72" s="165"/>
+      <c r="I72" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J72" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B28</f>
+        <v>52139</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A73" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E20</f>
+        <v>록소핀정 60mg</v>
+      </c>
+      <c r="C73" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D73" s="61">
+        <f>'시트2 32품목 스티커'!N20</f>
+        <v>125</v>
+      </c>
+      <c r="G73" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H73" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E28</f>
+        <v>에이토바정 20mg</v>
+      </c>
+      <c r="I73" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J73" s="61">
+        <f>'시트2 32품목 스티커'!N28</f>
+        <v>712</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A74" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B74" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D20</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C74" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74" s="62">
+        <f>'시트2 32품목 스티커'!H20</f>
+        <v>0</v>
+      </c>
+      <c r="G74" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H74" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D28</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I74" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J74" s="62">
+        <f>'시트2 32품목 스티커'!H28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A75" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="59">
+        <f>'시트2 32품목 스티커'!J20</f>
+        <v>0</v>
+      </c>
+      <c r="C75" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D75" s="61">
+        <f>'시트2 32품목 스티커'!K20</f>
+        <v>0</v>
+      </c>
+      <c r="G75" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H75" s="59">
+        <f>'시트2 32품목 스티커'!J28</f>
+        <v>0</v>
+      </c>
+      <c r="I75" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J75" s="61">
+        <f>'시트2 32품목 스티커'!K28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A76" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="63">
+        <f>'시트2 32품목 스티커'!I20</f>
+        <v>0</v>
+      </c>
+      <c r="C76" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D76" s="61"/>
+      <c r="G76" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" s="63">
+        <f>'시트2 32품목 스티커'!I28</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J76" s="61"/>
+    </row>
+    <row r="77" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A77" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="59">
+        <f>'시트2 32품목 스티커'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="C77" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D77" s="61"/>
+      <c r="G77" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H77" s="64">
+        <f>'시트2 32품목 스티커'!G28</f>
+        <v>0</v>
+      </c>
+      <c r="I77" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J77" s="61"/>
+    </row>
+    <row r="78" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="79" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A79" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B79" s="165"/>
+      <c r="C79" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D79" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B21</f>
+        <v>54810</v>
+      </c>
+      <c r="G79" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H79" s="165"/>
+      <c r="I79" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J79" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B29</f>
+        <v>52138</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A80" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B80" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E21</f>
+        <v>록소핀정 80mg</v>
+      </c>
+      <c r="C80" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D80" s="61">
+        <f>'시트2 32품목 스티커'!N21</f>
+        <v>125</v>
+      </c>
+      <c r="G80" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H80" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E29</f>
+        <v>에이토바정 20mg</v>
+      </c>
+      <c r="I80" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J80" s="61">
+        <f>'시트2 32품목 스티커'!N29</f>
+        <v>712</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A81" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B81" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D21</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C81" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D81" s="62">
+        <f>'시트2 32품목 스티커'!H21</f>
+        <v>0</v>
+      </c>
+      <c r="G81" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H81" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D29</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I81" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J81" s="62">
+        <f>'시트2 32품목 스티커'!H29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A82" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B82" s="59">
+        <f>'시트2 32품목 스티커'!J21</f>
+        <v>0</v>
+      </c>
+      <c r="C82" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" s="61">
+        <f>'시트2 32품목 스티커'!K21</f>
+        <v>0</v>
+      </c>
+      <c r="G82" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H82" s="59">
+        <f>'시트2 32품목 스티커'!J29</f>
+        <v>0</v>
+      </c>
+      <c r="I82" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J82" s="61">
+        <f>'시트2 32품목 스티커'!K29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A83" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" s="63">
+        <f>'시트2 32품목 스티커'!I21</f>
+        <v>0</v>
+      </c>
+      <c r="C83" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D83" s="61"/>
+      <c r="G83" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83" s="63">
+        <f>'시트2 32품목 스티커'!I29</f>
+        <v>0</v>
+      </c>
+      <c r="I83" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J83" s="61"/>
+    </row>
+    <row r="84" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A84" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" s="59">
+        <f>'시트2 32품목 스티커'!G21</f>
+        <v>0</v>
+      </c>
+      <c r="C84" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D84" s="61"/>
+      <c r="G84" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H84" s="59">
+        <f>'시트2 32품목 스티커'!G29</f>
+        <v>0</v>
+      </c>
+      <c r="I84" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J84" s="61"/>
+    </row>
+    <row r="85" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="86" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A86" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B86" s="165"/>
+      <c r="C86" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D86" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B22</f>
+        <v>54692</v>
+      </c>
+      <c r="G86" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H86" s="165"/>
+      <c r="I86" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J86" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B30</f>
+        <v>53521</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A87" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B87" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E22</f>
+        <v>사포레서방정 300mg</v>
+      </c>
+      <c r="C87" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D87" s="61">
+        <f>'시트2 32품목 스티커'!N22</f>
+        <v>1050</v>
+      </c>
+      <c r="G87" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H87" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E30</f>
+        <v>에페나정 50mg</v>
+      </c>
+      <c r="I87" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J87" s="61">
+        <f>'시트2 32품목 스티커'!N30</f>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A88" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B88" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D22</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C88" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D88" s="62">
+        <f>'시트2 32품목 스티커'!H22</f>
+        <v>0</v>
+      </c>
+      <c r="G88" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H88" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D30</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I88" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J88" s="62">
+        <f>'시트2 32품목 스티커'!H30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A89" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B89" s="59">
+        <f>'시트2 32품목 스티커'!J22</f>
+        <v>0</v>
+      </c>
+      <c r="C89" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D89" s="61">
+        <f>'시트2 32품목 스티커'!K22</f>
+        <v>0</v>
+      </c>
+      <c r="G89" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H89" s="59">
+        <f>'시트2 32품목 스티커'!J30</f>
+        <v>0</v>
+      </c>
+      <c r="I89" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J89" s="61">
+        <f>'시트2 32품목 스티커'!K30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A90" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" s="63">
+        <f>'시트2 32품목 스티커'!I22</f>
+        <v>0</v>
+      </c>
+      <c r="C90" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D90" s="61"/>
+      <c r="G90" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H90" s="63">
+        <f>'시트2 32품목 스티커'!I30</f>
+        <v>0</v>
+      </c>
+      <c r="I90" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J90" s="61"/>
+    </row>
+    <row r="91" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A91" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B91" s="59">
+        <f>'시트2 32품목 스티커'!G22</f>
+        <v>0</v>
+      </c>
+      <c r="C91" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D91" s="61"/>
+      <c r="G91" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H91" s="59">
+        <f>'시트2 32품목 스티커'!G30</f>
+        <v>0</v>
+      </c>
+      <c r="I91" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J91" s="61"/>
+    </row>
+    <row r="92" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="93" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A93" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B93" s="165"/>
+      <c r="C93" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D93" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B23</f>
+        <v>54691</v>
+      </c>
+      <c r="G93" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H93" s="165"/>
+      <c r="I93" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J93" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B31</f>
+        <v>51305</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A94" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B94" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E23</f>
+        <v>사포레서방정 300mg</v>
+      </c>
+      <c r="C94" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D94" s="61">
+        <f>'시트2 32품목 스티커'!N23</f>
+        <v>1050</v>
+      </c>
+      <c r="G94" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H94" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E31</f>
+        <v>오메나정 20mg</v>
+      </c>
+      <c r="I94" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J94" s="61">
+        <f>'시트2 32품목 스티커'!N31</f>
+        <v>764</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A95" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B95" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D23</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C95" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D95" s="62">
+        <f>'시트2 32품목 스티커'!H23</f>
+        <v>0</v>
+      </c>
+      <c r="G95" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H95" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D31</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I95" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J95" s="62">
+        <f>'시트2 32품목 스티커'!H31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A96" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B96" s="59">
+        <f>'시트2 32품목 스티커'!J23</f>
+        <v>0</v>
+      </c>
+      <c r="C96" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D96" s="61">
+        <f>'시트2 32품목 스티커'!K23</f>
+        <v>0</v>
+      </c>
+      <c r="G96" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H96" s="59">
+        <f>'시트2 32품목 스티커'!J31</f>
+        <v>0</v>
+      </c>
+      <c r="I96" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J96" s="61">
+        <f>'시트2 32품목 스티커'!K31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A97" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" s="63">
+        <f>'시트2 32품목 스티커'!I23</f>
+        <v>0</v>
+      </c>
+      <c r="C97" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D97" s="61"/>
+      <c r="G97" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H97" s="63">
+        <f>'시트2 32품목 스티커'!I31</f>
+        <v>0</v>
+      </c>
+      <c r="I97" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J97" s="61"/>
+    </row>
+    <row r="98" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A98" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B98" s="59">
+        <f>'시트2 32품목 스티커'!G23</f>
+        <v>0</v>
+      </c>
+      <c r="C98" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D98" s="61"/>
+      <c r="G98" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H98" s="59">
+        <f>'시트2 32품목 스티커'!G31</f>
+        <v>0</v>
+      </c>
+      <c r="I98" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J98" s="61"/>
+    </row>
+    <row r="99" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="100" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A100" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B100" s="165"/>
+      <c r="C100" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D100" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B24</f>
+        <v>53687</v>
+      </c>
+      <c r="G100" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H100" s="165"/>
+      <c r="I100" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J100" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B32</f>
+        <v>51306</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A101" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B101" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E24</f>
+        <v>스토렌정</v>
+      </c>
+      <c r="C101" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D101" s="61">
+        <f>'시트2 32품목 스티커'!N24</f>
+        <v>124</v>
+      </c>
+      <c r="G101" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H101" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E32</f>
+        <v>오메나정 40mg</v>
+      </c>
+      <c r="I101" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J101" s="61">
+        <f>'시트2 32품목 스티커'!N32</f>
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A102" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B102" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D24</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C102" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D102" s="62">
+        <f>'시트2 32품목 스티커'!H24</f>
+        <v>0</v>
+      </c>
+      <c r="G102" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H102" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D32</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I102" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J102" s="62">
+        <f>'시트2 32품목 스티커'!H32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A103" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B103" s="59">
+        <f>'시트2 32품목 스티커'!J24</f>
+        <v>0</v>
+      </c>
+      <c r="C103" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D103" s="61">
+        <f>'시트2 32품목 스티커'!K24</f>
+        <v>0</v>
+      </c>
+      <c r="G103" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H103" s="59">
+        <f>'시트2 32품목 스티커'!J32</f>
+        <v>0</v>
+      </c>
+      <c r="I103" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J103" s="61">
+        <f>'시트2 32품목 스티커'!K32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A104" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" s="63">
+        <f>'시트2 32품목 스티커'!I24</f>
+        <v>0</v>
+      </c>
+      <c r="C104" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D104" s="61"/>
+      <c r="G104" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H104" s="63">
+        <f>'시트2 32품목 스티커'!I32</f>
+        <v>0</v>
+      </c>
+      <c r="I104" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J104" s="61"/>
+    </row>
+    <row r="105" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A105" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B105" s="59">
+        <f>'시트2 32품목 스티커'!G24</f>
+        <v>0</v>
+      </c>
+      <c r="C105" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D105" s="61"/>
+      <c r="G105" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H105" s="64">
+        <f>'시트2 32품목 스티커'!G32</f>
+        <v>0</v>
+      </c>
+      <c r="I105" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J105" s="61"/>
+    </row>
+    <row r="106" spans="1:10" ht="13.7" customHeight="1"/>
+    <row r="107" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A107" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="B107" s="165"/>
+      <c r="C107" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D107" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B25</f>
+        <v>51318</v>
+      </c>
+      <c r="G107" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H107" s="165"/>
+      <c r="I107" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="J107" s="57" t="str">
+        <f>'시트2 32품목 스티커'!B33</f>
+        <v>51309</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A108" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B108" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E25</f>
+        <v>아세네정</v>
+      </c>
+      <c r="C108" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D108" s="61">
+        <f>'시트2 32품목 스티커'!N25</f>
+        <v>188</v>
+      </c>
+      <c r="G108" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H108" s="59" t="str">
+        <f>'시트2 32품목 스티커'!E33</f>
+        <v>이코녹스정 100mg</v>
+      </c>
+      <c r="I108" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J108" s="61">
+        <f>'시트2 32품목 스티커'!N33</f>
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A109" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B109" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D25</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="C109" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D109" s="62">
+        <f>'시트2 32품목 스티커'!H25</f>
+        <v>0</v>
+      </c>
+      <c r="G109" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="H109" s="59" t="str">
+        <f>'시트2 32품목 스티커'!D33</f>
+        <v>(유) 한풍제약</v>
+      </c>
+      <c r="I109" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J109" s="62">
+        <f>'시트2 32품목 스티커'!H33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A110" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="B110" s="59">
+        <f>'시트2 32품목 스티커'!J25</f>
+        <v>0</v>
+      </c>
+      <c r="C110" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D110" s="61">
+        <f>'시트2 32품목 스티커'!K25</f>
+        <v>0</v>
+      </c>
+      <c r="G110" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H110" s="59">
+        <f>'시트2 32품목 스티커'!J33</f>
+        <v>0</v>
+      </c>
+      <c r="I110" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="J110" s="61">
+        <f>'시트2 32품목 스티커'!K33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A111" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B111" s="63">
+        <f>'시트2 32품목 스티커'!I25</f>
+        <v>0</v>
+      </c>
+      <c r="C111" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D111" s="61"/>
+      <c r="G111" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H111" s="63">
+        <f>'시트2 32품목 스티커'!I33</f>
+        <v>0</v>
+      </c>
+      <c r="I111" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="J111" s="61"/>
+    </row>
+    <row r="112" spans="1:10" ht="13.7" customHeight="1">
+      <c r="A112" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B112" s="59">
+        <f>'시트2 32품목 스티커'!G25</f>
+        <v>0</v>
+      </c>
+      <c r="C112" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D112" s="61"/>
+      <c r="G112" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H112" s="59">
+        <f>'시트2 32품목 스티커'!G33</f>
+        <v>0</v>
+      </c>
+      <c r="I112" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="J112" s="61"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <autoFilter ref="A2:J6"/>
-  <mergeCells count="2">
+  <mergeCells count="32">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="G100:H100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.34027777777777779" right="0.22013888888888888" top="0.64027777777777772" bottom="0.22013888888888888" header="0.51180555555555551" footer="0.51180555555555551"/>
